--- a/Res_ConvLSTM/DroughtDataset_model_testing_1753718880_h_7.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1753718880_h_7.xlsx
@@ -652,13 +652,13 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.02990317759476907</v>
+        <v>0.02106837795059541</v>
       </c>
       <c r="B2" t="n">
-        <v>0.008438437034621818</v>
+        <v>0.008426604091929184</v>
       </c>
       <c r="C2" t="n">
-        <v>44190846</v>
+        <v>6346380</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>44190846</v>
+        <v>6346380</v>
       </c>
       <c r="K2" t="n">
-        <v>29784283</v>
+        <v>4144769</v>
       </c>
       <c r="L2" t="n">
-        <v>15670964</v>
+        <v>2092327</v>
       </c>
       <c r="M2" t="n">
-        <v>3511271</v>
+        <v>453534</v>
       </c>
       <c r="N2" t="n">
-        <v>111638</v>
+        <v>13298</v>
       </c>
       <c r="O2" t="n">
-        <v>2128797</v>
+        <v>279275</v>
       </c>
       <c r="P2" t="n">
-        <v>842704</v>
+        <v>111463</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999949932098389</v>
+        <v>0.9999963641166687</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8320595622062683</v>
+        <v>0.8044283986091614</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6733850836753845</v>
+        <v>0.6264577507972717</v>
       </c>
       <c r="T2" t="n">
-        <v>0.5886211395263672</v>
+        <v>0.530832827091217</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1628643870353699</v>
+        <v>0.1378173977136612</v>
       </c>
       <c r="V2" t="n">
-        <v>0.6475912928581238</v>
+        <v>0.5944386124610901</v>
       </c>
       <c r="W2" t="n">
-        <v>0.7589261531829834</v>
+        <v>0.712046205997467</v>
       </c>
       <c r="X2" t="n">
-        <v>44190846</v>
+        <v>6346380</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,469 +742,469 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>44190846</v>
+        <v>6346380</v>
       </c>
       <c r="AF2" t="n">
-        <v>33659447</v>
+        <v>4822613</v>
       </c>
       <c r="AG2" t="n">
-        <v>20826834</v>
+        <v>3003787</v>
       </c>
       <c r="AH2" t="n">
-        <v>5601637</v>
+        <v>802859</v>
       </c>
       <c r="AI2" t="n">
-        <v>413079</v>
+        <v>59182</v>
       </c>
       <c r="AJ2" t="n">
-        <v>3215114</v>
+        <v>460006</v>
       </c>
       <c r="AK2" t="n">
-        <v>1260508</v>
+        <v>180185</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9563413858413696</v>
+        <v>0.9558094143867493</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9113937020301819</v>
+        <v>0.9115616083145142</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8582093119621277</v>
+        <v>0.8578552603721619</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6620789766311646</v>
+        <v>0.6612218618392944</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9020217657089233</v>
+        <v>0.9019814133644104</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.931441068649292</v>
+        <v>0.9314774870872498</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.007596801735837281</v>
+        <v>0.005089000659220995</v>
       </c>
       <c r="B3" t="n">
-        <v>0.00202340465893989</v>
+        <v>0.00201955565764127</v>
       </c>
       <c r="C3" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>29784283</v>
+        <v>4144769</v>
       </c>
       <c r="E3" t="n">
-        <v>5200529</v>
+        <v>862233</v>
       </c>
       <c r="F3" t="n">
-        <v>143737</v>
+        <v>26129</v>
       </c>
       <c r="G3" t="n">
-        <v>11244</v>
+        <v>1964</v>
       </c>
       <c r="H3" t="n">
-        <v>10720</v>
+        <v>1865</v>
       </c>
       <c r="I3" t="n">
-        <v>761</v>
+        <v>96</v>
       </c>
       <c r="J3" t="n">
-        <v>70116133</v>
+        <v>10069597</v>
       </c>
       <c r="K3" t="n">
-        <v>73144340</v>
+        <v>10371271</v>
       </c>
       <c r="L3" t="n">
-        <v>83818290</v>
+        <v>11866515</v>
       </c>
       <c r="M3" t="n">
-        <v>105320345</v>
+        <v>15078073</v>
       </c>
       <c r="N3" t="n">
-        <v>113108917</v>
+        <v>16243173</v>
       </c>
       <c r="O3" t="n">
-        <v>109582496</v>
+        <v>15715000</v>
       </c>
       <c r="P3" t="n">
-        <v>112685982</v>
+        <v>16177417</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8473169207572937</v>
+        <v>0.8228551149368286</v>
       </c>
       <c r="S3" t="n">
-        <v>0.68468177318573</v>
+        <v>0.6336776614189148</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5374768972396851</v>
+        <v>0.4839869439601898</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1787766963243484</v>
+        <v>0.1483572274446487</v>
       </c>
       <c r="V3" t="n">
-        <v>0.5969291925430298</v>
+        <v>0.5471024513244629</v>
       </c>
       <c r="W3" t="n">
-        <v>0.622596263885498</v>
+        <v>0.5760153532028198</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>33659447</v>
+        <v>4822613</v>
       </c>
       <c r="Z3" t="n">
-        <v>1384204</v>
+        <v>198886</v>
       </c>
       <c r="AA3" t="n">
-        <v>59560</v>
+        <v>8613</v>
       </c>
       <c r="AB3" t="n">
-        <v>47621</v>
+        <v>6871</v>
       </c>
       <c r="AC3" t="n">
-        <v>247</v>
+        <v>45</v>
       </c>
       <c r="AD3" t="n">
-        <v>210</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>70116354</v>
+        <v>10069620</v>
       </c>
       <c r="AF3" t="n">
-        <v>77619300</v>
+        <v>11155975</v>
       </c>
       <c r="AG3" t="n">
-        <v>89394449</v>
+        <v>12822698</v>
       </c>
       <c r="AH3" t="n">
-        <v>106848837</v>
+        <v>15345889</v>
       </c>
       <c r="AI3" t="n">
-        <v>113471912</v>
+        <v>16296043</v>
       </c>
       <c r="AJ3" t="n">
-        <v>110391725</v>
+        <v>15855549</v>
       </c>
       <c r="AK3" t="n">
-        <v>112860888</v>
+        <v>16209238</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9575594067573547</v>
+        <v>0.9574265480041504</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9099474549293518</v>
+        <v>0.9097204804420471</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8574531674385071</v>
+        <v>0.8567676544189453</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6615032553672791</v>
+        <v>0.660255491733551</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9015399217605591</v>
+        <v>0.9011561870574951</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9312731623649597</v>
+        <v>0.9311549663543701</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.06901253756728558</v>
+        <v>0.05516128976784697</v>
       </c>
       <c r="B4" t="n">
-        <v>0.03193072151668488</v>
+        <v>0.0318933357951476</v>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5615220</v>
+        <v>942458</v>
       </c>
       <c r="E4" t="n">
-        <v>15670964</v>
+        <v>2092327</v>
       </c>
       <c r="F4" t="n">
-        <v>1364677</v>
+        <v>224234</v>
       </c>
       <c r="G4" t="n">
-        <v>70913</v>
+        <v>12541</v>
       </c>
       <c r="H4" t="n">
-        <v>149604</v>
+        <v>27393</v>
       </c>
       <c r="I4" t="n">
-        <v>16572</v>
+        <v>2925</v>
       </c>
       <c r="J4" t="n">
-        <v>221</v>
+        <v>23</v>
       </c>
       <c r="K4" t="n">
-        <v>6011571</v>
+        <v>1007671</v>
       </c>
       <c r="L4" t="n">
-        <v>7600957</v>
+        <v>1247606</v>
       </c>
       <c r="M4" t="n">
-        <v>2453977</v>
+        <v>400848</v>
       </c>
       <c r="N4" t="n">
-        <v>573828</v>
+        <v>83192</v>
       </c>
       <c r="O4" t="n">
-        <v>1158457</v>
+        <v>190538</v>
       </c>
       <c r="P4" t="n">
-        <v>267686</v>
+        <v>45076</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999974966049194</v>
+        <v>0.999998152256012</v>
       </c>
       <c r="R4" t="n">
-        <v>0.839618980884552</v>
+        <v>0.8135373592376709</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6789864897727966</v>
+        <v>0.6300470232963562</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5618876218795776</v>
+        <v>0.5063286423683167</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1704499870538712</v>
+        <v>0.1428932249546051</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6212291121482849</v>
+        <v>0.5697891116142273</v>
       </c>
       <c r="W4" t="n">
-        <v>0.6840346455574036</v>
+        <v>0.6368477344512939</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1434717</v>
+        <v>208181</v>
       </c>
       <c r="Z4" t="n">
-        <v>20826834</v>
+        <v>3003787</v>
       </c>
       <c r="AA4" t="n">
-        <v>579437</v>
+        <v>83142</v>
       </c>
       <c r="AB4" t="n">
-        <v>38501</v>
+        <v>5553</v>
       </c>
       <c r="AC4" t="n">
-        <v>7988</v>
+        <v>1148</v>
       </c>
       <c r="AD4" t="n">
-        <v>476</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1536611</v>
+        <v>222967</v>
       </c>
       <c r="AG4" t="n">
-        <v>2024798</v>
+        <v>291423</v>
       </c>
       <c r="AH4" t="n">
-        <v>925485</v>
+        <v>133032</v>
       </c>
       <c r="AI4" t="n">
-        <v>210833</v>
+        <v>30322</v>
       </c>
       <c r="AJ4" t="n">
-        <v>349228</v>
+        <v>49989</v>
       </c>
       <c r="AK4" t="n">
-        <v>92780</v>
+        <v>13255</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9569499492645264</v>
+        <v>0.9566173553466797</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9106699824333191</v>
+        <v>0.9106400609016418</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8578310608863831</v>
+        <v>0.8573110699653625</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6617910265922546</v>
+        <v>0.6607382893562317</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9017807841300964</v>
+        <v>0.9015686511993408</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313570857048035</v>
+        <v>0.9313161373138428</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>277900</v>
+        <v>46647</v>
       </c>
       <c r="E5" t="n">
-        <v>1993350</v>
+        <v>314453</v>
       </c>
       <c r="F5" t="n">
-        <v>3511271</v>
+        <v>453534</v>
       </c>
       <c r="G5" t="n">
-        <v>186849</v>
+        <v>27384</v>
       </c>
       <c r="H5" t="n">
-        <v>506266</v>
+        <v>84530</v>
       </c>
       <c r="I5" t="n">
-        <v>57232</v>
+        <v>10530</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>5367006</v>
+        <v>892289</v>
       </c>
       <c r="L5" t="n">
-        <v>7216989</v>
+        <v>1209552</v>
       </c>
       <c r="M5" t="n">
-        <v>3021607</v>
+        <v>483545</v>
       </c>
       <c r="N5" t="n">
-        <v>512817</v>
+        <v>76337</v>
       </c>
       <c r="O5" t="n">
-        <v>1437450</v>
+        <v>231187</v>
       </c>
       <c r="P5" t="n">
-        <v>510828</v>
+        <v>82044</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999980926513672</v>
+        <v>0.9999985694885254</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9004561901092529</v>
+        <v>0.8842616677284241</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8703673481941223</v>
+        <v>0.8503193259239197</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9520976543426514</v>
+        <v>0.9461261630058289</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9904936552047729</v>
+        <v>0.9902821183204651</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9772900938987732</v>
+        <v>0.9743101000785828</v>
       </c>
       <c r="W5" t="n">
-        <v>0.99318927526474</v>
+        <v>0.9922563433647156</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>56186</v>
+        <v>8150</v>
       </c>
       <c r="Z5" t="n">
-        <v>596891</v>
+        <v>86254</v>
       </c>
       <c r="AA5" t="n">
-        <v>5601637</v>
+        <v>802859</v>
       </c>
       <c r="AB5" t="n">
-        <v>69704</v>
+        <v>9996</v>
       </c>
       <c r="AC5" t="n">
-        <v>204029</v>
+        <v>29187</v>
       </c>
       <c r="AD5" t="n">
-        <v>4431</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1491842</v>
+        <v>214445</v>
       </c>
       <c r="AG5" t="n">
-        <v>2061119</v>
+        <v>298092</v>
       </c>
       <c r="AH5" t="n">
-        <v>931241</v>
+        <v>134220</v>
       </c>
       <c r="AI5" t="n">
-        <v>211376</v>
+        <v>30453</v>
       </c>
       <c r="AJ5" t="n">
-        <v>351133</v>
+        <v>50456</v>
       </c>
       <c r="AK5" t="n">
-        <v>93024</v>
+        <v>13322</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9735060334205627</v>
+        <v>0.9733545184135437</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9642549753189087</v>
+        <v>0.9640889763832092</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9837567210197449</v>
+        <v>0.9837200045585632</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963063597679138</v>
+        <v>0.9962978363037109</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9938730001449585</v>
+        <v>0.9938812851905823</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983745217323303</v>
+        <v>0.9983810186386108</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>44</v>
+        <v>7</v>
       </c>
       <c r="D6" t="n">
-        <v>100784</v>
+        <v>15724</v>
       </c>
       <c r="E6" t="n">
-        <v>148249</v>
+        <v>22481</v>
       </c>
       <c r="F6" t="n">
-        <v>185204</v>
+        <v>26015</v>
       </c>
       <c r="G6" t="n">
-        <v>111638</v>
+        <v>13298</v>
       </c>
       <c r="H6" t="n">
-        <v>70486</v>
+        <v>10743</v>
       </c>
       <c r="I6" t="n">
-        <v>8050</v>
+        <v>1367</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>45337</v>
+        <v>6580</v>
       </c>
       <c r="Z6" t="n">
-        <v>37466</v>
+        <v>5392</v>
       </c>
       <c r="AA6" t="n">
-        <v>76329</v>
+        <v>11005</v>
       </c>
       <c r="AB6" t="n">
-        <v>413079</v>
+        <v>59182</v>
       </c>
       <c r="AC6" t="n">
-        <v>48877</v>
+        <v>6995</v>
       </c>
       <c r="AD6" t="n">
-        <v>3367</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>17198</v>
+        <v>2781</v>
       </c>
       <c r="E7" t="n">
-        <v>238835</v>
+        <v>44754</v>
       </c>
       <c r="F7" t="n">
-        <v>711853</v>
+        <v>115764</v>
       </c>
       <c r="G7" t="n">
-        <v>284440</v>
+        <v>37730</v>
       </c>
       <c r="H7" t="n">
-        <v>2128797</v>
+        <v>279275</v>
       </c>
       <c r="I7" t="n">
-        <v>185071</v>
+        <v>30158</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>175</v>
+        <v>28</v>
       </c>
       <c r="Z7" t="n">
-        <v>5670</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>207844</v>
+        <v>29939</v>
       </c>
       <c r="AB7" t="n">
-        <v>53148</v>
+        <v>7636</v>
       </c>
       <c r="AC7" t="n">
-        <v>3215114</v>
+        <v>460006</v>
       </c>
       <c r="AD7" t="n">
-        <v>84296</v>
+        <v>12043</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>96</v>
+        <v>12</v>
       </c>
       <c r="D8" t="n">
-        <v>469</v>
+        <v>61</v>
       </c>
       <c r="E8" t="n">
-        <v>19994</v>
+        <v>3685</v>
       </c>
       <c r="F8" t="n">
-        <v>48506</v>
+        <v>8706</v>
       </c>
       <c r="G8" t="n">
-        <v>20382</v>
+        <v>3573</v>
       </c>
       <c r="H8" t="n">
-        <v>421381</v>
+        <v>66007</v>
       </c>
       <c r="I8" t="n">
-        <v>842704</v>
+        <v>111463</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>196</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>567</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>2315</v>
+        <v>333</v>
       </c>
       <c r="AB8" t="n">
-        <v>1859</v>
+        <v>266</v>
       </c>
       <c r="AC8" t="n">
-        <v>88087</v>
+        <v>12614</v>
       </c>
       <c r="AD8" t="n">
-        <v>1260508</v>
+        <v>180185</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
